--- a/nba_stats_CLE_NYK_ECF_G2_20260521.xlsx
+++ b/nba_stats_CLE_NYK_ECF_G2_20260521.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1042,33 +1042,25 @@
           <t>インディアナ大出身。ハム筋負傷からECF G1で復帰、3&amp;D駒</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I7" s="10" t="n">
+        <v>34</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N7" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -1444,10 +1436,8 @@
           <t>ウェストバージニア大出身。Deuceの愛称、対人守備の切り札</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I11" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>0</v>
@@ -1458,15 +1448,11 @@
       <c r="L11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
@@ -1552,36 +1538,16 @@
           <t>ジョージア工科大出身。2月にペリカンズから加入、闘犬PG</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="18" t="n"/>
+      <c r="N12" s="18" t="n"/>
       <c r="O12" s="14" t="inlineStr">
         <is>
           <t>—</t>
@@ -1676,25 +1642,17 @@
           <t>ウィチタ州立大出身。3P39%超のシューター</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I13" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -3040,23 +2998,17 @@
           <t>ドイツ出身。2/1にSACから加入、25年EuroBasket MVP</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I29" s="14" t="n">
+        <v>18</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>4</v>
       </c>
       <c r="M29" s="14" t="n">
         <v>5</v>
@@ -3291,10 +3243,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J31" s="14" t="n">
+        <v>6</v>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
@@ -3409,28 +3359,30 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>カンザス州立大出身。ストレッチ4、G1で4Pプレー成功</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>9+</t>
-        </is>
+          <t>カンザス州立大出身。ストレッチ4、G1で29分10点5R3A</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>29</v>
       </c>
       <c r="J32" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
@@ -3495,71 +3447,51 @@
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="11" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>ロンゾ・ボール</t>
+          <t>ジェイロン・タイソン</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>196cm</t>
+          <t>198cm</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>86kg</t>
+          <t>98kg</t>
         </is>
       </c>
       <c r="F33" s="11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>8年目</t>
+          <t>2年目</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>UCLA出身。シーズン序盤に攻撃面で苦戦、ローテ外時期も</t>
-        </is>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K33" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L33" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M33" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N33" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>カリフォルニア大出身。G1ではDNP-CD</t>
+        </is>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
       <c r="O33" s="14" t="inlineStr">
         <is>
           <t>—</t>
@@ -3623,39 +3555,39 @@
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="7" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ジェイロン・タイソン</t>
+          <t>クレイグ・ポーター Jr.</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>198cm</t>
+          <t>188cm</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>98kg</t>
+          <t>84kg</t>
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>2年目</t>
+          <t>3年目</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>カリフォルニア大出身。G1ではDNP-CD</t>
+          <t>ウィチタ州立大出身。3番手PG</t>
         </is>
       </c>
       <c r="I34" s="15" t="inlineStr">
@@ -3731,11 +3663,11 @@
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="11" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>クレイグ・ポーター Jr.</t>
+          <t>タイリース・プロクター</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3745,25 +3677,25 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>188cm</t>
+          <t>193cm</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>84kg</t>
+          <t>86kg</t>
         </is>
       </c>
       <c r="F35" s="11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>3年目</t>
+          <t>1年目</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>ウィチタ州立大出身。3番手PG</t>
+          <t>デューク大出身。25年ドラフト49位のルーキー</t>
         </is>
       </c>
       <c r="I35" s="17" t="inlineStr">
@@ -3839,30 +3771,30 @@
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="7" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>タイリース・プロクター</t>
+          <t>サリオ・ニャン</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>193cm</t>
+          <t>198cm</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>86kg</t>
+          <t>89kg</t>
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -3871,7 +3803,7 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>デューク大出身。25年ドラフト49位のルーキー</t>
+          <t>セネガル/イタリア出身。25年ドラフト58位のルーキー</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
@@ -3945,126 +3877,19 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>サリオ・ニャン</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>198cm</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>89kg</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>1年目</t>
-        </is>
-      </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>セネガル/イタリア出身。25年ドラフト58位のルーキー</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="J37" s="18" t="n"/>
-      <c r="K37" s="18" t="n"/>
-      <c r="L37" s="18" t="n"/>
-      <c r="M37" s="18" t="n"/>
-      <c r="N37" s="18" t="n"/>
-      <c r="O37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="33">
     <mergeCell ref="U16:Z16"/>
-    <mergeCell ref="I37:N37"/>
     <mergeCell ref="I22:N22"/>
     <mergeCell ref="I18:N18"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="I3:N3"/>
     <mergeCell ref="O22:T22"/>
+    <mergeCell ref="I12:N12"/>
     <mergeCell ref="U7:Z7"/>
     <mergeCell ref="U3:Z3"/>
     <mergeCell ref="O16:T16"/>
+    <mergeCell ref="I33:N33"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="U18:Z18"/>
     <mergeCell ref="A22:C22"/>
